--- a/assets/data/recipes/foodProperties.xlsx
+++ b/assets/data/recipes/foodProperties.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a1pab\Desktop\Pablo\showtime\assets\data\recipes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E53D74D2-DEDC-4EFA-9C00-411E8AEF9EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86E7AFA-AF7E-4173-B57E-21AA25202472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="106">
   <si>
     <t>Ingredient</t>
   </si>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t>merluza</t>
+  </si>
+  <si>
+    <t>passata</t>
   </si>
 </sst>
 </file>
@@ -714,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" style="1" customWidth="1"/>
@@ -2704,202 +2707,157 @@
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="B46">
-        <v>371</v>
+        <v>21</v>
       </c>
       <c r="C46">
-        <v>1.51</v>
+        <v>0.2</v>
       </c>
       <c r="D46">
-        <v>74.67</v>
+        <v>3</v>
       </c>
       <c r="E46">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="F46">
-        <v>13.04</v>
-      </c>
-      <c r="H46">
-        <v>1</v>
-      </c>
-      <c r="I46">
-        <v>0.30399999999999999</v>
-      </c>
-      <c r="J46">
-        <v>5.36</v>
-      </c>
-      <c r="X46">
-        <v>3.21</v>
+        <v>1.3</v>
+      </c>
+      <c r="G46">
+        <v>530</v>
+      </c>
+      <c r="P46">
+        <v>8</v>
+      </c>
+      <c r="U46">
+        <v>16</v>
+      </c>
+      <c r="V46">
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="B47">
-        <v>673</v>
+        <v>371</v>
       </c>
       <c r="C47">
-        <v>68.400000000000006</v>
+        <v>1.51</v>
       </c>
       <c r="D47">
-        <v>13.1</v>
+        <v>74.67</v>
       </c>
       <c r="E47">
-        <v>3.59</v>
+        <v>2.7</v>
       </c>
       <c r="F47">
-        <v>13.7</v>
-      </c>
-      <c r="G47">
+        <v>13.04</v>
+      </c>
+      <c r="H47">
         <v>1</v>
       </c>
-      <c r="H47">
-        <v>0.36399999999999999</v>
-      </c>
       <c r="I47">
-        <v>0.22700000000000001</v>
+        <v>0.30399999999999999</v>
       </c>
       <c r="J47">
-        <v>4.3899999999999997</v>
-      </c>
-      <c r="K47">
-        <v>0.313</v>
-      </c>
-      <c r="L47">
-        <v>9.4E-2</v>
-      </c>
-      <c r="N47">
-        <v>34</v>
-      </c>
-      <c r="P47">
-        <v>0.8</v>
-      </c>
-      <c r="R47">
-        <v>9.33</v>
-      </c>
-      <c r="S47">
-        <v>53.9</v>
-      </c>
-      <c r="T47">
-        <v>597</v>
-      </c>
-      <c r="U47">
-        <v>16</v>
-      </c>
-      <c r="V47">
-        <v>575</v>
-      </c>
-      <c r="W47">
-        <v>251</v>
+        <v>5.36</v>
       </c>
       <c r="X47">
-        <v>5.53</v>
-      </c>
-      <c r="Y47">
-        <v>6.45</v>
-      </c>
-      <c r="Z47">
-        <v>1.32</v>
-      </c>
-      <c r="AA47">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="AB47">
-        <v>0.7</v>
-      </c>
-      <c r="AC47">
-        <v>2</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B48">
-        <v>263</v>
+        <v>673</v>
       </c>
       <c r="C48">
-        <v>21.2</v>
+        <v>68.400000000000006</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="F48">
-        <v>16.899999999999999</v>
+        <v>13.7</v>
       </c>
       <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="I48">
+        <v>0.22700000000000001</v>
+      </c>
+      <c r="J48">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="K48">
+        <v>0.313</v>
+      </c>
+      <c r="L48">
+        <v>9.4E-2</v>
+      </c>
+      <c r="N48">
+        <v>34</v>
+      </c>
+      <c r="P48">
+        <v>0.8</v>
+      </c>
+      <c r="R48">
+        <v>9.33</v>
+      </c>
+      <c r="S48">
+        <v>53.9</v>
+      </c>
+      <c r="T48">
+        <v>597</v>
+      </c>
+      <c r="U48">
+        <v>16</v>
+      </c>
+      <c r="V48">
+        <v>575</v>
+      </c>
+      <c r="W48">
+        <v>251</v>
+      </c>
+      <c r="X48">
+        <v>5.53</v>
+      </c>
+      <c r="Y48">
+        <v>6.45</v>
+      </c>
+      <c r="Z48">
+        <v>1.32</v>
+      </c>
+      <c r="AA48">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="AB48">
+        <v>0.7</v>
+      </c>
+      <c r="AC48">
         <v>2</v>
-      </c>
-      <c r="H48">
-        <v>0.73199999999999998</v>
-      </c>
-      <c r="I48">
-        <v>0.23499999999999999</v>
-      </c>
-      <c r="J48">
-        <v>4.34</v>
-      </c>
-      <c r="K48">
-        <v>0.66800000000000004</v>
-      </c>
-      <c r="L48">
-        <v>0.38300000000000001</v>
-      </c>
-      <c r="N48">
-        <v>5</v>
-      </c>
-      <c r="O48">
-        <v>0.7</v>
-      </c>
-      <c r="P48">
-        <v>0.7</v>
-      </c>
-      <c r="T48">
-        <v>287</v>
-      </c>
-      <c r="U48">
-        <v>14</v>
-      </c>
-      <c r="V48">
-        <v>175</v>
-      </c>
-      <c r="W48">
-        <v>19</v>
-      </c>
-      <c r="X48">
-        <v>0.88</v>
-      </c>
-      <c r="Y48">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="Z48">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="AA48">
-        <v>0.01</v>
-      </c>
-      <c r="AB48">
-        <v>24.6</v>
-      </c>
-      <c r="AC48">
-        <v>56</v>
       </c>
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="B49">
-        <v>180</v>
+        <v>263</v>
       </c>
       <c r="C49">
-        <v>16</v>
+        <v>21.2</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2908,277 +2866,283 @@
         <v>0</v>
       </c>
       <c r="F49">
-        <v>11</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="G49">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="H49">
-        <v>0.44</v>
+        <v>0.73199999999999998</v>
       </c>
       <c r="I49">
-        <v>0.14000000000000001</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="J49">
-        <v>2.6</v>
+        <v>4.34</v>
       </c>
       <c r="K49">
-        <v>0.4</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="L49">
-        <v>0.22</v>
+        <v>0.38300000000000001</v>
       </c>
       <c r="N49">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O49">
-        <v>0.42</v>
+        <v>0.7</v>
       </c>
       <c r="P49">
-        <v>0.42</v>
+        <v>0.7</v>
       </c>
       <c r="T49">
-        <v>172</v>
+        <v>287</v>
       </c>
       <c r="U49">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="V49">
-        <v>105</v>
+        <v>175</v>
       </c>
       <c r="W49">
-        <v>11.4</v>
+        <v>19</v>
       </c>
       <c r="X49">
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
       <c r="Y49">
-        <v>1.32</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="Z49">
-        <v>2.7E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="AA49">
-        <v>6.0000000000000001E-3</v>
+        <v>0.01</v>
       </c>
       <c r="AB49">
-        <v>14.76</v>
+        <v>24.6</v>
       </c>
       <c r="AC49">
-        <v>33.6</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="B50">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="C50">
-        <v>0.26</v>
+        <v>16</v>
       </c>
       <c r="D50">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E50">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="F50">
-        <v>1.81</v>
+        <v>11</v>
+      </c>
+      <c r="G50">
+        <v>1.2</v>
       </c>
       <c r="H50">
-        <v>5.0999999999999997E-2</v>
+        <v>0.44</v>
+      </c>
+      <c r="I50">
+        <v>0.14000000000000001</v>
       </c>
       <c r="J50">
-        <v>1.58</v>
+        <v>2.6</v>
+      </c>
+      <c r="K50">
+        <v>0.4</v>
       </c>
       <c r="L50">
-        <v>0.14499999999999999</v>
+        <v>0.22</v>
+      </c>
+      <c r="N50">
+        <v>3</v>
+      </c>
+      <c r="O50">
+        <v>0.42</v>
       </c>
       <c r="P50">
-        <v>23.3</v>
-      </c>
-      <c r="S50">
-        <v>0.8</v>
+        <v>0.42</v>
       </c>
       <c r="T50">
-        <v>446</v>
+        <v>172</v>
       </c>
       <c r="U50">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="V50">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="W50">
-        <v>22.3</v>
+        <v>11.4</v>
       </c>
       <c r="X50">
-        <v>0.37</v>
+        <v>0.5</v>
       </c>
       <c r="Y50">
-        <v>0.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z50">
-        <v>0.13</v>
+        <v>2.7E-2</v>
       </c>
       <c r="AA50">
-        <v>0.16</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="AB50">
-        <v>2</v>
+        <v>14.76</v>
       </c>
       <c r="AC50">
-        <v>2</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B51">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="C51">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="D51">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E51">
-        <v>2.8</v>
+        <v>0.65</v>
       </c>
       <c r="F51">
-        <v>1</v>
-      </c>
-      <c r="G51">
-        <v>426</v>
+        <v>1.81</v>
       </c>
       <c r="H51">
-        <v>0.05</v>
-      </c>
-      <c r="I51">
-        <v>0.11</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="J51">
-        <v>0.6</v>
-      </c>
-      <c r="K51">
-        <v>0.29799999999999999</v>
+        <v>1.58</v>
       </c>
       <c r="L51">
-        <v>6.0999999999999999E-2</v>
-      </c>
-      <c r="N51">
-        <v>16</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="P51">
-        <v>9</v>
-      </c>
-      <c r="R51">
-        <v>1.06</v>
+        <v>23.3</v>
       </c>
       <c r="S51">
-        <v>1.1000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="T51">
-        <v>340</v>
+        <v>446</v>
       </c>
       <c r="U51">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="V51">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="W51">
-        <v>12</v>
+        <v>22.3</v>
       </c>
       <c r="X51">
-        <v>0.8</v>
+        <v>0.37</v>
       </c>
       <c r="Y51">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="Z51">
-        <v>0.127</v>
+        <v>0.13</v>
       </c>
       <c r="AA51">
-        <v>0.125</v>
+        <v>0.16</v>
       </c>
       <c r="AB51">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="AC51">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B52">
-        <v>359</v>
+        <v>26</v>
       </c>
       <c r="C52">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="D52">
-        <v>79.8</v>
+        <v>7</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="F52">
-        <v>6.94</v>
+        <v>1</v>
+      </c>
+      <c r="G52">
+        <v>426</v>
       </c>
       <c r="H52">
-        <v>0.16300000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="I52">
-        <v>1.2999999999999999E-2</v>
+        <v>0.11</v>
       </c>
       <c r="J52">
-        <v>1.48</v>
+        <v>0.6</v>
       </c>
       <c r="K52">
-        <v>0.39</v>
+        <v>0.29799999999999999</v>
       </c>
       <c r="L52">
-        <v>9.2999999999999999E-2</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="N52">
-        <v>97</v>
+        <v>16</v>
+      </c>
+      <c r="P52">
+        <v>9</v>
       </c>
       <c r="R52">
-        <v>0.04</v>
+        <v>1.06</v>
+      </c>
+      <c r="S52">
+        <v>1.1000000000000001</v>
       </c>
       <c r="T52">
-        <v>35</v>
+        <v>340</v>
       </c>
       <c r="U52">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="V52">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W52">
         <v>12</v>
       </c>
       <c r="X52">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="Y52">
-        <v>0.49</v>
+        <v>0.32</v>
       </c>
       <c r="Z52">
-        <v>6.9000000000000006E-2</v>
+        <v>0.127</v>
       </c>
       <c r="AA52">
-        <v>0.47199999999999998</v>
+        <v>0.125</v>
       </c>
       <c r="AB52">
-        <v>7.5</v>
+        <v>0.3</v>
       </c>
       <c r="AC52">
         <v>1</v>
@@ -3186,304 +3150,355 @@
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="B53">
-        <v>270</v>
+        <v>359</v>
       </c>
       <c r="C53">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="D53">
-        <v>49</v>
+        <v>79.8</v>
       </c>
       <c r="E53">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>9.4</v>
+        <v>6.94</v>
       </c>
       <c r="H53">
-        <v>0.50700000000000001</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="I53">
-        <v>0.24</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="J53">
-        <v>4.76</v>
+        <v>1.48</v>
       </c>
       <c r="K53">
-        <v>0.54800000000000004</v>
+        <v>0.39</v>
       </c>
       <c r="L53">
-        <v>9.1999999999999998E-2</v>
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="N53">
+        <v>97</v>
+      </c>
+      <c r="R53">
+        <v>0.04</v>
       </c>
       <c r="T53">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="U53">
-        <v>211</v>
+        <v>10</v>
       </c>
       <c r="V53">
-        <v>113</v>
+        <v>43</v>
       </c>
       <c r="W53">
-        <v>26.9</v>
+        <v>12</v>
       </c>
       <c r="X53">
-        <v>3.36</v>
+        <v>1.2</v>
       </c>
       <c r="Y53">
-        <v>0.88</v>
+        <v>0.49</v>
       </c>
       <c r="Z53">
-        <v>0.124</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="AA53">
-        <v>0.63200000000000001</v>
+        <v>0.47199999999999998</v>
       </c>
       <c r="AB53">
-        <v>23.2</v>
+        <v>7.5</v>
       </c>
       <c r="AC53">
-        <v>400</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B54">
+        <v>270</v>
+      </c>
+      <c r="C54">
+        <v>3.6</v>
+      </c>
+      <c r="D54">
         <v>49</v>
       </c>
-      <c r="B54">
-        <v>367</v>
-      </c>
-      <c r="C54">
-        <v>3</v>
-      </c>
-      <c r="D54">
-        <v>77</v>
-      </c>
       <c r="E54">
-        <v>40</v>
+        <v>5.3</v>
       </c>
       <c r="F54">
-        <v>7</v>
+        <v>9.4</v>
+      </c>
+      <c r="H54">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="I54">
+        <v>0.24</v>
+      </c>
+      <c r="J54">
+        <v>4.76</v>
+      </c>
+      <c r="K54">
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="L54">
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="T54">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="U54">
-        <v>30</v>
+        <v>211</v>
+      </c>
+      <c r="V54">
+        <v>113</v>
+      </c>
+      <c r="W54">
+        <v>26.9</v>
       </c>
       <c r="X54">
-        <v>1.0900000000000001</v>
+        <v>3.36</v>
+      </c>
+      <c r="Y54">
+        <v>0.88</v>
+      </c>
+      <c r="Z54">
+        <v>0.124</v>
+      </c>
+      <c r="AA54">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="AB54">
+        <v>23.2</v>
       </c>
       <c r="AC54">
-        <v>106</v>
+        <v>400</v>
       </c>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="B55">
-        <v>36</v>
+        <v>367</v>
       </c>
       <c r="C55">
-        <v>0.22</v>
+        <v>3</v>
       </c>
       <c r="D55">
-        <v>7.96</v>
+        <v>77</v>
       </c>
       <c r="E55">
-        <v>4.8600000000000003</v>
+        <v>40</v>
       </c>
       <c r="F55">
-        <v>0.64</v>
-      </c>
-      <c r="M55">
-        <v>3.7</v>
-      </c>
-      <c r="P55">
-        <v>59.6</v>
+        <v>7</v>
       </c>
       <c r="T55">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="U55">
-        <v>17</v>
-      </c>
-      <c r="V55">
-        <v>23</v>
-      </c>
-      <c r="W55">
-        <v>12.5</v>
+        <v>30</v>
       </c>
       <c r="X55">
-        <v>0.26</v>
-      </c>
-      <c r="Y55">
-        <v>0.11</v>
-      </c>
-      <c r="Z55">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="AA55">
-        <v>0.36799999999999999</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="AC55">
-        <v>2</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="B56">
-        <v>385</v>
+        <v>36</v>
       </c>
       <c r="C56">
-        <v>0.32</v>
+        <v>0.22</v>
       </c>
       <c r="D56">
-        <v>99.7</v>
+        <v>7.96</v>
       </c>
       <c r="E56">
-        <v>99.7</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="F56">
-        <v>0</v>
-      </c>
-      <c r="I56">
-        <v>1.9E-2</v>
+        <v>0.64</v>
+      </c>
+      <c r="M56">
+        <v>3.7</v>
+      </c>
+      <c r="P56">
+        <v>59.6</v>
       </c>
       <c r="T56">
+        <v>161</v>
+      </c>
+      <c r="U56">
+        <v>17</v>
+      </c>
+      <c r="V56">
+        <v>23</v>
+      </c>
+      <c r="W56">
+        <v>12.5</v>
+      </c>
+      <c r="X56">
+        <v>0.26</v>
+      </c>
+      <c r="Y56">
+        <v>0.11</v>
+      </c>
+      <c r="Z56">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AA56">
+        <v>0.36799999999999999</v>
+      </c>
+      <c r="AC56">
         <v>2</v>
-      </c>
-      <c r="U56">
-        <v>1</v>
-      </c>
-      <c r="X56">
-        <v>0.05</v>
-      </c>
-      <c r="Y56">
-        <v>0.01</v>
-      </c>
-      <c r="Z56">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="AB56">
-        <v>0.6</v>
-      </c>
-      <c r="AC56">
-        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B57">
-        <v>18</v>
+        <v>385</v>
       </c>
       <c r="C57">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="D57">
-        <v>3.9</v>
+        <v>99.7</v>
       </c>
       <c r="E57">
-        <v>2.6</v>
+        <v>99.7</v>
       </c>
       <c r="F57">
-        <v>0.9</v>
-      </c>
-      <c r="G57">
-        <v>42</v>
-      </c>
-      <c r="H57">
-        <v>3.6999999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="I57">
         <v>1.9E-2</v>
       </c>
-      <c r="J57">
-        <v>0.59399999999999997</v>
-      </c>
-      <c r="K57">
-        <v>8.8999999999999996E-2</v>
-      </c>
-      <c r="L57">
-        <v>0.08</v>
-      </c>
-      <c r="M57">
-        <v>0.7</v>
-      </c>
-      <c r="N57">
-        <v>15</v>
-      </c>
-      <c r="P57">
-        <v>13.7</v>
-      </c>
-      <c r="R57">
-        <v>0.54</v>
-      </c>
-      <c r="S57">
-        <v>7.9</v>
-      </c>
       <c r="T57">
-        <v>237</v>
+        <v>2</v>
       </c>
       <c r="U57">
-        <v>10</v>
-      </c>
-      <c r="V57">
-        <v>24</v>
-      </c>
-      <c r="W57">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="X57">
-        <v>0.27</v>
+        <v>0.05</v>
       </c>
       <c r="Y57">
-        <v>0.17</v>
+        <v>0.01</v>
       </c>
       <c r="Z57">
-        <v>5.8999999999999997E-2</v>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="AB57">
+        <v>0.6</v>
       </c>
       <c r="AC57">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="B58">
-        <v>884</v>
+        <v>18</v>
       </c>
       <c r="C58">
-        <v>100</v>
+        <v>0.2</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>0.9</v>
+      </c>
+      <c r="G58">
+        <v>42</v>
+      </c>
+      <c r="H58">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="I58">
+        <v>1.9E-2</v>
+      </c>
+      <c r="J58">
+        <v>0.59399999999999997</v>
+      </c>
+      <c r="K58">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="L58">
+        <v>0.08</v>
+      </c>
+      <c r="M58">
+        <v>0.7</v>
+      </c>
+      <c r="N58">
+        <v>15</v>
+      </c>
+      <c r="P58">
+        <v>13.7</v>
+      </c>
+      <c r="R58">
+        <v>0.54</v>
+      </c>
+      <c r="S58">
+        <v>7.9</v>
+      </c>
+      <c r="T58">
+        <v>237</v>
+      </c>
+      <c r="U58">
+        <v>10</v>
+      </c>
+      <c r="V58">
+        <v>24</v>
+      </c>
+      <c r="W58">
+        <v>11</v>
+      </c>
+      <c r="X58">
+        <v>0.27</v>
+      </c>
+      <c r="Y58">
+        <v>0.17</v>
+      </c>
+      <c r="Z58">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="AC58">
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B59">
+        <v>884</v>
+      </c>
+      <c r="C59">
         <v>100</v>
-      </c>
-      <c r="B59">
-        <v>18</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -3497,92 +3512,112 @@
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B60">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="C60">
-        <v>4.4800000000000004</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="E60">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="F60">
-        <v>3.82</v>
-      </c>
-      <c r="G60">
-        <v>48</v>
-      </c>
-      <c r="H60">
-        <v>5.5E-2</v>
-      </c>
-      <c r="I60">
-        <v>0.24299999999999999</v>
-      </c>
-      <c r="J60">
-        <v>0.13500000000000001</v>
-      </c>
-      <c r="L60">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="M60">
-        <v>3</v>
-      </c>
-      <c r="Q60">
-        <v>0.78</v>
-      </c>
-      <c r="S60">
-        <v>0.2</v>
-      </c>
-      <c r="T60">
-        <v>164</v>
-      </c>
-      <c r="U60">
-        <v>127</v>
-      </c>
-      <c r="V60">
-        <v>101</v>
-      </c>
-      <c r="W60">
-        <v>11.4</v>
-      </c>
-      <c r="X60">
-        <v>0.05</v>
-      </c>
-      <c r="Y60">
-        <v>0.43</v>
-      </c>
-      <c r="Z60">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="AA60">
-        <v>2E-3</v>
-      </c>
-      <c r="AC60">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B61">
+        <v>78</v>
+      </c>
+      <c r="C61">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="D61">
+        <v>5.57</v>
+      </c>
+      <c r="E61">
+        <v>4.09</v>
+      </c>
+      <c r="F61">
+        <v>3.82</v>
+      </c>
+      <c r="G61">
+        <v>48</v>
+      </c>
+      <c r="H61">
+        <v>5.5E-2</v>
+      </c>
+      <c r="I61">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="J61">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="L61">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="M61">
+        <v>3</v>
+      </c>
+      <c r="Q61">
+        <v>0.78</v>
+      </c>
+      <c r="S61">
+        <v>0.2</v>
+      </c>
+      <c r="T61">
+        <v>164</v>
+      </c>
+      <c r="U61">
+        <v>127</v>
+      </c>
+      <c r="V61">
+        <v>101</v>
+      </c>
+      <c r="W61">
+        <v>11.4</v>
+      </c>
+      <c r="X61">
+        <v>0.05</v>
+      </c>
+      <c r="Y61">
+        <v>0.43</v>
+      </c>
+      <c r="Z61">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="AA61">
+        <v>2E-3</v>
+      </c>
+      <c r="AC61">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A62" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="B61">
+      <c r="B62">
         <v>19.8</v>
       </c>
-      <c r="C61">
+      <c r="C62">
         <v>0.22</v>
       </c>
-      <c r="D61">
+      <c r="D62">
         <v>4.1500000000000004</v>
       </c>
-      <c r="E61">
+      <c r="E62">
         <v>2.15</v>
       </c>
-      <c r="F61">
+      <c r="F62">
         <v>1.5</v>
       </c>
     </row>
@@ -3647,7 +3682,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G61 H49:AC49">
+  <conditionalFormatting sqref="G4:G62 H50:AC50">
     <cfRule type="colorScale" priority="45">
       <colorScale>
         <cfvo type="min"/>
@@ -3659,7 +3694,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G62:G1048576 G1:G56 H57:H61 H49:AC49">
+  <conditionalFormatting sqref="G63:G1048576 G1:G57 H58:H62 H50:AC50">
     <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="min"/>
@@ -3671,7 +3706,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H62:H1048576 H1:H48 I57:I61 H50:H56">
+  <conditionalFormatting sqref="H63:H1048576 H1:H49 I58:I62 H51:H57">
     <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
@@ -3683,7 +3718,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I62:I1048576 I1:I48 J57:J61 I50:I56">
+  <conditionalFormatting sqref="I63:I1048576 I1:I49 J58:J62 I51:I57">
     <cfRule type="colorScale" priority="55">
       <colorScale>
         <cfvo type="min"/>
@@ -3695,7 +3730,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J62:J1048576 J1:J48 J50:J56">
+  <conditionalFormatting sqref="J63:J1048576 J1:J49 J51:J57">
     <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
@@ -3707,7 +3742,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K50:K1048576 K1:K48">
+  <conditionalFormatting sqref="K51:K1048576 K1:K49">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
@@ -3719,7 +3754,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L50:L1048576 L1:L48">
+  <conditionalFormatting sqref="L51:L1048576 L1:L49">
     <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="min"/>
@@ -3731,7 +3766,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M50:M1048576 M1:M48">
+  <conditionalFormatting sqref="M51:M1048576 M1:M49">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
@@ -3743,7 +3778,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N50:N1048576 N1:N48">
+  <conditionalFormatting sqref="N51:N1048576 N1:N49">
     <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
@@ -3755,7 +3790,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O50:O1048576 O1:O48">
+  <conditionalFormatting sqref="O51:O1048576 O1:O49">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
@@ -3767,7 +3802,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P50:P1048576 P1:P48">
+  <conditionalFormatting sqref="P51:P1048576 P1:P49">
     <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
@@ -3779,7 +3814,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q50:Q1048576 Q1:Q48">
+  <conditionalFormatting sqref="Q51:Q1048576 Q1:Q49">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
@@ -3791,7 +3826,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R50:R1048576 R1:R48">
+  <conditionalFormatting sqref="R51:R1048576 R1:R49">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -3803,7 +3838,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S50:S1048576 S1:S48">
+  <conditionalFormatting sqref="S51:S1048576 S1:S49">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
@@ -3815,7 +3850,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T50:T1048576 T1:T48">
+  <conditionalFormatting sqref="T51:T1048576 T1:T49">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -3827,7 +3862,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U50:U1048576 U1:U48">
+  <conditionalFormatting sqref="U51:U1048576 U1:U49">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -3839,7 +3874,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V50:V1048576 V1:V48">
+  <conditionalFormatting sqref="V51:V1048576 V1:V49">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -3851,7 +3886,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W50:W1048576 W1:W48">
+  <conditionalFormatting sqref="W51:W1048576 W1:W49">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -3863,7 +3898,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X50:X1048576 X1:X48">
+  <conditionalFormatting sqref="X51:X1048576 X1:X49">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -3875,7 +3910,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y50:Y1048576 Y1:Y48">
+  <conditionalFormatting sqref="Y51:Y1048576 Y1:Y49">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -3887,7 +3922,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z50:Z1048576 Z1:Z48">
+  <conditionalFormatting sqref="Z51:Z1048576 Z1:Z49">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -3899,7 +3934,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA50:AA1048576 AA1:AA48">
+  <conditionalFormatting sqref="AA51:AA1048576 AA1:AA49">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -3911,7 +3946,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB50:AB1048576 AB1:AB48">
+  <conditionalFormatting sqref="AB51:AB1048576 AB1:AB49">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -3923,7 +3958,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC50:AC1048576 AC1:AC48">
+  <conditionalFormatting sqref="AC51:AC1048576 AC1:AC49">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>

--- a/assets/data/recipes/foodProperties.xlsx
+++ b/assets/data/recipes/foodProperties.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a1pab\Desktop\Pablo\showtime\assets\data\recipes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pabloac\Desktop\Pablo\showtime\assets\data\recipes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86E7AFA-AF7E-4173-B57E-21AA25202472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B9AEFD-B789-485E-8B06-B4E9E4C9F040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="107">
   <si>
     <t>Ingredient</t>
   </si>
@@ -354,13 +354,16 @@
   </si>
   <si>
     <t>passata</t>
+  </si>
+  <si>
+    <t>prawns</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -370,6 +373,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -427,7 +438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -437,6 +448,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -717,8 +729,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AC63"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="5.5703125" customWidth="1"/>
@@ -3070,150 +3082,136 @@
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="B52">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="C52">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="D52">
-        <v>7</v>
+        <v>0.48</v>
       </c>
       <c r="E52">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="F52">
+        <v>15.6</v>
+      </c>
+      <c r="G52">
         <v>1</v>
       </c>
-      <c r="G52">
-        <v>426</v>
-      </c>
-      <c r="H52">
-        <v>0.05</v>
-      </c>
-      <c r="I52">
-        <v>0.11</v>
-      </c>
-      <c r="J52">
-        <v>0.6</v>
-      </c>
-      <c r="K52">
-        <v>0.29799999999999999</v>
-      </c>
-      <c r="L52">
-        <v>6.0999999999999999E-2</v>
-      </c>
-      <c r="N52">
-        <v>16</v>
-      </c>
-      <c r="P52">
-        <v>9</v>
-      </c>
-      <c r="R52">
-        <v>1.06</v>
-      </c>
-      <c r="S52">
-        <v>1.1000000000000001</v>
-      </c>
+      <c r="O52">
+        <v>1</v>
+      </c>
+      <c r="P52" s="9"/>
       <c r="T52">
-        <v>340</v>
+        <v>146</v>
       </c>
       <c r="U52">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="V52">
-        <v>44</v>
+        <v>191</v>
       </c>
       <c r="W52">
-        <v>12</v>
+        <v>22.5</v>
       </c>
       <c r="X52">
-        <v>0.8</v>
+        <v>0.52</v>
       </c>
       <c r="Y52">
-        <v>0.32</v>
+        <v>0.94</v>
       </c>
       <c r="Z52">
-        <v>0.127</v>
+        <v>0.2</v>
       </c>
       <c r="AA52">
-        <v>0.125</v>
+        <v>0.02</v>
       </c>
       <c r="AB52">
-        <v>0.3</v>
+        <v>19.5</v>
       </c>
       <c r="AC52">
-        <v>1</v>
+        <v>475</v>
       </c>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B53">
-        <v>359</v>
+        <v>26</v>
       </c>
       <c r="C53">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="D53">
-        <v>79.8</v>
+        <v>7</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="F53">
-        <v>6.94</v>
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <v>426</v>
       </c>
       <c r="H53">
-        <v>0.16300000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="I53">
-        <v>1.2999999999999999E-2</v>
+        <v>0.11</v>
       </c>
       <c r="J53">
-        <v>1.48</v>
+        <v>0.6</v>
       </c>
       <c r="K53">
-        <v>0.39</v>
+        <v>0.29799999999999999</v>
       </c>
       <c r="L53">
-        <v>9.2999999999999999E-2</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="N53">
-        <v>97</v>
+        <v>16</v>
+      </c>
+      <c r="P53">
+        <v>9</v>
       </c>
       <c r="R53">
-        <v>0.04</v>
+        <v>1.06</v>
+      </c>
+      <c r="S53">
+        <v>1.1000000000000001</v>
       </c>
       <c r="T53">
-        <v>35</v>
+        <v>340</v>
       </c>
       <c r="U53">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="V53">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W53">
         <v>12</v>
       </c>
       <c r="X53">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="Y53">
-        <v>0.49</v>
+        <v>0.32</v>
       </c>
       <c r="Z53">
-        <v>6.9000000000000006E-2</v>
+        <v>0.127</v>
       </c>
       <c r="AA53">
-        <v>0.47199999999999998</v>
+        <v>0.125</v>
       </c>
       <c r="AB53">
-        <v>7.5</v>
+        <v>0.3</v>
       </c>
       <c r="AC53">
         <v>1</v>
@@ -3221,304 +3219,355 @@
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="B54">
-        <v>270</v>
+        <v>359</v>
       </c>
       <c r="C54">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="D54">
-        <v>49</v>
+        <v>79.8</v>
       </c>
       <c r="E54">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="F54">
-        <v>9.4</v>
+        <v>6.94</v>
       </c>
       <c r="H54">
-        <v>0.50700000000000001</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="I54">
-        <v>0.24</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="J54">
-        <v>4.76</v>
+        <v>1.48</v>
       </c>
       <c r="K54">
-        <v>0.54800000000000004</v>
+        <v>0.39</v>
       </c>
       <c r="L54">
-        <v>9.1999999999999998E-2</v>
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="N54">
+        <v>97</v>
+      </c>
+      <c r="R54">
+        <v>0.04</v>
       </c>
       <c r="T54">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="U54">
-        <v>211</v>
+        <v>10</v>
       </c>
       <c r="V54">
-        <v>113</v>
+        <v>43</v>
       </c>
       <c r="W54">
-        <v>26.9</v>
+        <v>12</v>
       </c>
       <c r="X54">
-        <v>3.36</v>
+        <v>1.2</v>
       </c>
       <c r="Y54">
-        <v>0.88</v>
+        <v>0.49</v>
       </c>
       <c r="Z54">
-        <v>0.124</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="AA54">
-        <v>0.63200000000000001</v>
+        <v>0.47199999999999998</v>
       </c>
       <c r="AB54">
-        <v>23.2</v>
+        <v>7.5</v>
       </c>
       <c r="AC54">
-        <v>400</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B55">
+        <v>270</v>
+      </c>
+      <c r="C55">
+        <v>3.6</v>
+      </c>
+      <c r="D55">
         <v>49</v>
       </c>
-      <c r="B55">
-        <v>367</v>
-      </c>
-      <c r="C55">
-        <v>3</v>
-      </c>
-      <c r="D55">
-        <v>77</v>
-      </c>
       <c r="E55">
-        <v>40</v>
+        <v>5.3</v>
       </c>
       <c r="F55">
-        <v>7</v>
+        <v>9.4</v>
+      </c>
+      <c r="H55">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="I55">
+        <v>0.24</v>
+      </c>
+      <c r="J55">
+        <v>4.76</v>
+      </c>
+      <c r="K55">
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="L55">
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="T55">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="U55">
-        <v>30</v>
+        <v>211</v>
+      </c>
+      <c r="V55">
+        <v>113</v>
+      </c>
+      <c r="W55">
+        <v>26.9</v>
       </c>
       <c r="X55">
-        <v>1.0900000000000001</v>
+        <v>3.36</v>
+      </c>
+      <c r="Y55">
+        <v>0.88</v>
+      </c>
+      <c r="Z55">
+        <v>0.124</v>
+      </c>
+      <c r="AA55">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="AB55">
+        <v>23.2</v>
       </c>
       <c r="AC55">
-        <v>106</v>
+        <v>400</v>
       </c>
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="B56">
-        <v>36</v>
+        <v>367</v>
       </c>
       <c r="C56">
-        <v>0.22</v>
+        <v>3</v>
       </c>
       <c r="D56">
-        <v>7.96</v>
+        <v>77</v>
       </c>
       <c r="E56">
-        <v>4.8600000000000003</v>
+        <v>40</v>
       </c>
       <c r="F56">
-        <v>0.64</v>
-      </c>
-      <c r="M56">
-        <v>3.7</v>
-      </c>
-      <c r="P56">
-        <v>59.6</v>
+        <v>7</v>
       </c>
       <c r="T56">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="U56">
-        <v>17</v>
-      </c>
-      <c r="V56">
-        <v>23</v>
-      </c>
-      <c r="W56">
-        <v>12.5</v>
+        <v>30</v>
       </c>
       <c r="X56">
-        <v>0.26</v>
-      </c>
-      <c r="Y56">
-        <v>0.11</v>
-      </c>
-      <c r="Z56">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="AA56">
-        <v>0.36799999999999999</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="AC56">
-        <v>2</v>
+        <v>106</v>
       </c>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="B57">
-        <v>385</v>
+        <v>36</v>
       </c>
       <c r="C57">
-        <v>0.32</v>
+        <v>0.22</v>
       </c>
       <c r="D57">
-        <v>99.7</v>
+        <v>7.96</v>
       </c>
       <c r="E57">
-        <v>99.7</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="F57">
-        <v>0</v>
-      </c>
-      <c r="I57">
-        <v>1.9E-2</v>
+        <v>0.64</v>
+      </c>
+      <c r="M57">
+        <v>3.7</v>
+      </c>
+      <c r="P57">
+        <v>59.6</v>
       </c>
       <c r="T57">
+        <v>161</v>
+      </c>
+      <c r="U57">
+        <v>17</v>
+      </c>
+      <c r="V57">
+        <v>23</v>
+      </c>
+      <c r="W57">
+        <v>12.5</v>
+      </c>
+      <c r="X57">
+        <v>0.26</v>
+      </c>
+      <c r="Y57">
+        <v>0.11</v>
+      </c>
+      <c r="Z57">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AA57">
+        <v>0.36799999999999999</v>
+      </c>
+      <c r="AC57">
         <v>2</v>
-      </c>
-      <c r="U57">
-        <v>1</v>
-      </c>
-      <c r="X57">
-        <v>0.05</v>
-      </c>
-      <c r="Y57">
-        <v>0.01</v>
-      </c>
-      <c r="Z57">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="AB57">
-        <v>0.6</v>
-      </c>
-      <c r="AC57">
-        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B58">
-        <v>18</v>
+        <v>385</v>
       </c>
       <c r="C58">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="D58">
-        <v>3.9</v>
+        <v>99.7</v>
       </c>
       <c r="E58">
-        <v>2.6</v>
+        <v>99.7</v>
       </c>
       <c r="F58">
-        <v>0.9</v>
-      </c>
-      <c r="G58">
-        <v>42</v>
-      </c>
-      <c r="H58">
-        <v>3.6999999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="I58">
         <v>1.9E-2</v>
       </c>
-      <c r="J58">
-        <v>0.59399999999999997</v>
-      </c>
-      <c r="K58">
-        <v>8.8999999999999996E-2</v>
-      </c>
-      <c r="L58">
-        <v>0.08</v>
-      </c>
-      <c r="M58">
-        <v>0.7</v>
-      </c>
-      <c r="N58">
-        <v>15</v>
-      </c>
-      <c r="P58">
-        <v>13.7</v>
-      </c>
-      <c r="R58">
-        <v>0.54</v>
-      </c>
-      <c r="S58">
-        <v>7.9</v>
-      </c>
       <c r="T58">
-        <v>237</v>
+        <v>2</v>
       </c>
       <c r="U58">
-        <v>10</v>
-      </c>
-      <c r="V58">
-        <v>24</v>
-      </c>
-      <c r="W58">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="X58">
-        <v>0.27</v>
+        <v>0.05</v>
       </c>
       <c r="Y58">
-        <v>0.17</v>
+        <v>0.01</v>
       </c>
       <c r="Z58">
-        <v>5.8999999999999997E-2</v>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="AB58">
+        <v>0.6</v>
       </c>
       <c r="AC58">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="B59">
-        <v>884</v>
+        <v>18</v>
       </c>
       <c r="C59">
-        <v>100</v>
+        <v>0.2</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>0.9</v>
+      </c>
+      <c r="G59">
+        <v>42</v>
+      </c>
+      <c r="H59">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="I59">
+        <v>1.9E-2</v>
+      </c>
+      <c r="J59">
+        <v>0.59399999999999997</v>
+      </c>
+      <c r="K59">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="L59">
+        <v>0.08</v>
+      </c>
+      <c r="M59">
+        <v>0.7</v>
+      </c>
+      <c r="N59">
+        <v>15</v>
+      </c>
+      <c r="P59">
+        <v>13.7</v>
+      </c>
+      <c r="R59">
+        <v>0.54</v>
+      </c>
+      <c r="S59">
+        <v>7.9</v>
+      </c>
+      <c r="T59">
+        <v>237</v>
+      </c>
+      <c r="U59">
+        <v>10</v>
+      </c>
+      <c r="V59">
+        <v>24</v>
+      </c>
+      <c r="W59">
+        <v>11</v>
+      </c>
+      <c r="X59">
+        <v>0.27</v>
+      </c>
+      <c r="Y59">
+        <v>0.17</v>
+      </c>
+      <c r="Z59">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="AC59">
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B60">
+        <v>884</v>
+      </c>
+      <c r="C60">
         <v>100</v>
-      </c>
-      <c r="B60">
-        <v>18</v>
-      </c>
-      <c r="C60">
-        <v>0</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -3532,92 +3581,112 @@
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B61">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="C61">
-        <v>4.4800000000000004</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="F61">
-        <v>3.82</v>
-      </c>
-      <c r="G61">
-        <v>48</v>
-      </c>
-      <c r="H61">
-        <v>5.5E-2</v>
-      </c>
-      <c r="I61">
-        <v>0.24299999999999999</v>
-      </c>
-      <c r="J61">
-        <v>0.13500000000000001</v>
-      </c>
-      <c r="L61">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="M61">
-        <v>3</v>
-      </c>
-      <c r="Q61">
-        <v>0.78</v>
-      </c>
-      <c r="S61">
-        <v>0.2</v>
-      </c>
-      <c r="T61">
-        <v>164</v>
-      </c>
-      <c r="U61">
-        <v>127</v>
-      </c>
-      <c r="V61">
-        <v>101</v>
-      </c>
-      <c r="W61">
-        <v>11.4</v>
-      </c>
-      <c r="X61">
-        <v>0.05</v>
-      </c>
-      <c r="Y61">
-        <v>0.43</v>
-      </c>
-      <c r="Z61">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="AA61">
-        <v>2E-3</v>
-      </c>
-      <c r="AC61">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B62">
+        <v>78</v>
+      </c>
+      <c r="C62">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="D62">
+        <v>5.57</v>
+      </c>
+      <c r="E62">
+        <v>4.09</v>
+      </c>
+      <c r="F62">
+        <v>3.82</v>
+      </c>
+      <c r="G62">
+        <v>48</v>
+      </c>
+      <c r="H62">
+        <v>5.5E-2</v>
+      </c>
+      <c r="I62">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="J62">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="L62">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="M62">
+        <v>3</v>
+      </c>
+      <c r="Q62">
+        <v>0.78</v>
+      </c>
+      <c r="S62">
+        <v>0.2</v>
+      </c>
+      <c r="T62">
+        <v>164</v>
+      </c>
+      <c r="U62">
+        <v>127</v>
+      </c>
+      <c r="V62">
+        <v>101</v>
+      </c>
+      <c r="W62">
+        <v>11.4</v>
+      </c>
+      <c r="X62">
+        <v>0.05</v>
+      </c>
+      <c r="Y62">
+        <v>0.43</v>
+      </c>
+      <c r="Z62">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="AA62">
+        <v>2E-3</v>
+      </c>
+      <c r="AC62">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="63" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A63" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="B62">
+      <c r="B63">
         <v>19.8</v>
       </c>
-      <c r="C62">
+      <c r="C63">
         <v>0.22</v>
       </c>
-      <c r="D62">
+      <c r="D63">
         <v>4.1500000000000004</v>
       </c>
-      <c r="E62">
+      <c r="E63">
         <v>2.15</v>
       </c>
-      <c r="F62">
+      <c r="F63">
         <v>1.5</v>
       </c>
     </row>
@@ -3682,7 +3751,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G62 H50:AC50">
+  <conditionalFormatting sqref="G4:G63 H50:AC50">
     <cfRule type="colorScale" priority="45">
       <colorScale>
         <cfvo type="min"/>
@@ -3694,7 +3763,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G63:G1048576 G1:G57 H58:H62 H50:AC50">
+  <conditionalFormatting sqref="G64:G1048576 G1:G58 H59:H63 H50:AC50">
     <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="min"/>
@@ -3706,7 +3775,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H63:H1048576 H1:H49 I58:I62 H51:H57">
+  <conditionalFormatting sqref="H64:H1048576 H1:H49 I59:I63 H51:H58">
     <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
@@ -3718,7 +3787,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I63:I1048576 I1:I49 J58:J62 I51:I57">
+  <conditionalFormatting sqref="I64:I1048576 I1:I49 J59:J63 I51:I58">
     <cfRule type="colorScale" priority="55">
       <colorScale>
         <cfvo type="min"/>
@@ -3730,7 +3799,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J63:J1048576 J1:J49 J51:J57">
+  <conditionalFormatting sqref="J64:J1048576 J1:J49 J51:J58">
     <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
